--- a/recursos/comercial/PLANILLA_REFERIDOS.xlsx
+++ b/recursos/comercial/PLANILLA_REFERIDOS.xlsx
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="H9" s="8">
-        <f>IFERROR(AVERAGE(IF(REFERIDOS!R3:R302&lt;&gt;"",REFERIDOS!R3:R302-REFERIDOS!B3:B302)),"")</f>
+        <f>IFERROR(SUMPRODUCT((REFERIDOS!R3:R302&lt;&gt;"")*(REFERIDOS!R3:R302-REFERIDOS!B3:B302))/COUNTA(REFERIDOS!R3:R302),"")</f>
         <v/>
       </c>
     </row>
